--- a/docs/demo/pack/kestrel-msel.xlsx
+++ b/docs/demo/pack/kestrel-msel.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objectives" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MSEL'!$A$1:$Q$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MSEL'!$A$1:$U$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Phases'!$A$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objectives'!$A$1:$C$5</definedName>
   </definedNames>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,10 @@
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,6 +564,26 @@
           <t>Pulse Media</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Pulse Media Alt</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Pulse Likes</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Pulse Reposts</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Pulse Replies</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -640,7 +664,11 @@
           <t>Lead Controller</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -721,7 +749,6 @@
           <t>SimCell - Utility</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -798,7 +825,11 @@
           <t>SimCell - EOC</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -880,6 +911,20 @@
           <t>news-mill-road.mp4</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>News footage of water gushing up through cracked pavement and flowing down a residential street toward a storm drain, as a utility truck with flashing amber lights pulls up.</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>386</v>
+      </c>
+      <c r="T5" t="n">
+        <v>254</v>
+      </c>
+      <c r="U5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -956,7 +1001,11 @@
           <t>SimCell - Utility</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1033,7 +1082,6 @@
           <t>SimCell - State</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1110,7 +1158,11 @@
           <t>SimCell - Health</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n"/>
+      <c r="U8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1191,7 +1243,6 @@
           <t>SimCell - EOC</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1273,6 +1324,20 @@
           <t>scoop-brown-tap.mp4</t>
         </is>
       </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Shaky phone video of cloudy, brownish water running from a kitchen faucet into a stainless steel sink.</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>962</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>718</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1349,7 +1414,6 @@
           <t>SimCell - Mass Care</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1426,7 +1490,17 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1507,7 +1581,6 @@
           <t>SimCell - Health</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1589,6 +1662,14 @@
           <t>pio-statement-card.png</t>
         </is>
       </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Official notice from Kestrel County Emergency Management. Boil water advisory, Zones 2 to 4. Boiling tap water for 1 minute is safe and effective. The advisory has not expanded: Zones 2, 3 and 4 only. Free bottled water at Elm Street Fire Station and Fairhaven High School. Official updates come only from verified accounts: KestrelCoEM and FairhavenWater.</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n"/>
+      <c r="U14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1665,7 +1746,6 @@
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1746,7 +1826,11 @@
           <t>SimCell - State</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n"/>
+      <c r="U16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1823,7 +1907,6 @@
           <t>SimCell - EOC</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1900,7 +1983,17 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>334</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1977,7 +2070,15 @@
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>418</v>
+      </c>
+      <c r="T19" t="n">
+        <v>297</v>
+      </c>
+      <c r="U19" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2058,7 +2159,11 @@
           <t>SimCell - Utility</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="n"/>
+      <c r="U20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2135,7 +2240,15 @@
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>228</v>
+      </c>
+      <c r="T21" t="n">
+        <v>176</v>
+      </c>
+      <c r="U21" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2212,7 +2325,11 @@
           <t>SimCell - Health</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2289,7 +2406,6 @@
           <t>SimCell - Mass Care</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2366,7 +2482,11 @@
           <t>SimCell - Utility</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2443,7 +2563,6 @@
           <t>SimCell - Utility</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2520,7 +2639,11 @@
           <t>SimCell - EOC</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2597,7 +2720,6 @@
           <t>SimCell - Health</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2678,7 +2800,11 @@
           <t>SimCell - State</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="n"/>
+      <c r="U28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2755,7 +2881,6 @@
           <t>SimCell - Mass Care</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2832,7 +2957,11 @@
           <t>Lead Controller</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="n"/>
+      <c r="U30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2909,7 +3038,6 @@
           <t>SimCell - Health</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2990,7 +3118,11 @@
           <t>Lead Controller</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="n"/>
+      <c r="U32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3067,7 +3199,6 @@
           <t>SimCell - EOC</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3144,7 +3275,11 @@
           <t>SimCell - Utility</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n"/>
+      <c r="U34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3225,10 +3360,9 @@
           <t>Lead Controller</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q35"/>
+  <autoFilter ref="A1:U35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/demo/pack/kestrel-msel.xlsx
+++ b/docs/demo/pack/kestrel-msel.xlsx
@@ -913,7 +913,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>News footage of water gushing up through cracked pavement and flowing down a residential street toward a storm drain, as a utility truck with flashing amber lights pulls up.</t>
+          <t>News footage of water surging up through the pavement and flooding a residential street. Down the road, a fire engine waits behind a "Road work ahead" sign and traffic cones, beside a line of stopped cars.</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Shaky phone video of cloudy, brownish water running from a kitchen faucet into a stainless steel sink.</t>
+          <t>Shaky close-up video of rust-brown tap water pouring from a chrome tap and filling a white bathroom sink.</t>
         </is>
       </c>
       <c r="S10" s="2" t="n">
